--- a/data/trans_dic/P17G_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P17G_R2-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un médico privado en su última visita</t>
+          <t>Población que consultó en las últimas 2 semanas a un/a médico/a privado/a (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,34</t>
+          <t>0,26; 1,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,58</t>
+          <t>0,32; 1,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,54</t>
+          <t>0,27; 1,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,03</t>
+          <t>0,09; 1,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,39</t>
+          <t>0,36; 1,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,35</t>
+          <t>0,38; 1,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,15</t>
+          <t>0,62; 2,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,37</t>
+          <t>0,35; 1,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,17</t>
+          <t>0,4; 1,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,23</t>
+          <t>0,44; 1,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,62</t>
+          <t>0,59; 1,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,99</t>
+          <t>0,3; 0,97</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,0</t>
+          <t>0,81; 1,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,94</t>
+          <t>0,8; 2,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,32</t>
+          <t>1,12; 2,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,08</t>
+          <t>0,83; 2,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,39</t>
+          <t>1,06; 2,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,36</t>
+          <t>0,4; 1,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,24</t>
+          <t>1,01; 2,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,13</t>
+          <t>1,03; 2,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,93</t>
+          <t>1,05; 1,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,45</t>
+          <t>0,73; 1,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,01</t>
+          <t>1,2; 2,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,9</t>
+          <t>1,09; 1,83</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,54</t>
+          <t>2,04; 5,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,48</t>
+          <t>1,27; 4,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 6,26</t>
+          <t>2,58; 6,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,06</t>
+          <t>2,61; 5,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 6,31</t>
+          <t>2,46; 6,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 6,64</t>
+          <t>2,6; 6,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 6,29</t>
+          <t>2,73; 6,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,56; 7,68</t>
+          <t>4,53; 7,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,2</t>
+          <t>2,59; 5,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,79</t>
+          <t>2,31; 5,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,16; 5,61</t>
+          <t>3,12; 5,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,98; 6,3</t>
+          <t>4,0; 6,37</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,88</t>
+          <t>1,03; 1,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,78</t>
+          <t>0,93; 1,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,36</t>
+          <t>1,41; 2,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,3</t>
+          <t>1,23; 2,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,12</t>
+          <t>1,27; 2,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,64</t>
+          <t>0,88; 1,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,37</t>
+          <t>1,43; 2,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,63</t>
+          <t>1,73; 2,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,84</t>
+          <t>1,23; 1,85</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 1,59</t>
+          <t>1,01; 1,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,2</t>
+          <t>1,55; 2,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,31</t>
+          <t>1,59; 2,34</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un médico privado en su última visita</t>
+          <t>Población que consultó en las últimas 2 semanas a un/a médico/a privado/a (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2809; 13802</t>
+          <t>2716; 12266</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3035; 15241</t>
+          <t>3072; 14048</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2010; 11584</t>
+          <t>2060; 12173</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>449; 5316</t>
+          <t>453; 5268</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4318; 18345</t>
+          <t>4676; 20145</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5095; 17971</t>
+          <t>5098; 17715</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5859; 21196</t>
+          <t>6072; 21939</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2742; 10313</t>
+          <t>2656; 10092</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10062; 27483</t>
+          <t>9305; 25679</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10659; 28104</t>
+          <t>10169; 27096</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9630; 28078</t>
+          <t>10208; 27410</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3970; 12539</t>
+          <t>3796; 12284</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12954; 33706</t>
+          <t>13659; 31464</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15449; 37829</t>
+          <t>15598; 39378</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22991; 48048</t>
+          <t>23198; 46846</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18253; 47533</t>
+          <t>19033; 49086</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16469; 37931</t>
+          <t>16751; 37271</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7073; 23750</t>
+          <t>7029; 22617</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20689; 44260</t>
+          <t>20004; 43245</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23355; 47706</t>
+          <t>23045; 48195</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34949; 63121</t>
+          <t>34475; 61905</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25402; 53555</t>
+          <t>26924; 55189</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48308; 81405</t>
+          <t>48387; 82468</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>49705; 85979</t>
+          <t>49297; 82646</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10889; 30556</t>
+          <t>11236; 30173</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6277; 21320</t>
+          <t>6068; 22204</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13308; 34211</t>
+          <t>14137; 34234</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17493; 39214</t>
+          <t>16898; 38478</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11914; 30041</t>
+          <t>11740; 30217</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11242; 30267</t>
+          <t>11850; 31280</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14841; 34542</t>
+          <t>14981; 35906</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30100; 50730</t>
+          <t>29914; 50755</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26828; 53398</t>
+          <t>26606; 53424</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20953; 44661</t>
+          <t>21503; 47839</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34669; 61519</t>
+          <t>34156; 62266</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>51959; 82352</t>
+          <t>52329; 83268</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33859; 61432</t>
+          <t>33614; 62190</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30754; 60470</t>
+          <t>31602; 62766</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45380; 79307</t>
+          <t>47548; 78161</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43098; 79409</t>
+          <t>42503; 81572</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>41338; 71712</t>
+          <t>42750; 74119</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31622; 57805</t>
+          <t>31069; 58840</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47791; 83290</t>
+          <t>50252; 85022</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>61475; 96033</t>
+          <t>63023; 97345</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>83093; 122514</t>
+          <t>81811; 123182</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>69861; 109971</t>
+          <t>69553; 107044</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>105809; 151308</t>
+          <t>106812; 153311</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>111579; 164071</t>
+          <t>112573; 166125</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P17G_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P17G_R2-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,19</t>
+          <t>0,27; 1,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,45</t>
+          <t>0,31; 1,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,62</t>
+          <t>0,27; 1,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,02</t>
+          <t>0,08; 0,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,53</t>
+          <t>0,34; 1,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,34</t>
+          <t>0,38; 1,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,23</t>
+          <t>0,58; 2,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,34</t>
+          <t>0,36; 1,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,1</t>
+          <t>0,41; 1,13</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,18</t>
+          <t>0,45; 1,22</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,58</t>
+          <t>0,58; 1,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,97</t>
+          <t>0,31; 1,0</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,86</t>
+          <t>0,8; 1,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,02</t>
+          <t>0,81; 1,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,26</t>
+          <t>1,07; 2,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,14</t>
+          <t>0,9; 2,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,35</t>
+          <t>1,05; 2,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,3</t>
+          <t>0,43; 1,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,19</t>
+          <t>0,99; 2,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,16</t>
+          <t>1,28; 2,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,89</t>
+          <t>1,03; 1,85</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,49</t>
+          <t>0,72; 1,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,04</t>
+          <t>1,18; 1,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 1,83</t>
+          <t>1,28; 2,07</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,47</t>
+          <t>2,0; 5,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,66</t>
+          <t>1,3; 4,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,26</t>
+          <t>2,56; 6,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,95</t>
+          <t>2,51; 5,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 6,86</t>
+          <t>2,62; 6,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,54</t>
+          <t>2,81; 6,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,53; 7,68</t>
+          <t>4,29; 7,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,2</t>
+          <t>2,71; 5,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,13</t>
+          <t>2,24; 4,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,12; 5,68</t>
+          <t>3,12; 5,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 6,37</t>
+          <t>3,87; 6,02</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,9</t>
+          <t>1,05; 1,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,85</t>
+          <t>0,92; 1,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,32</t>
+          <t>1,39; 2,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,36</t>
+          <t>1,38; 2,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,19</t>
+          <t>1,22; 2,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,67</t>
+          <t>0,9; 1,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,42</t>
+          <t>1,42; 2,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,67</t>
+          <t>1,89; 2,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,85</t>
+          <t>1,26; 1,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 1,55</t>
+          <t>1,02; 1,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,23</t>
+          <t>1,52; 2,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,34</t>
+          <t>1,74; 2,42</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7327</t>
+          <t>7872</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2716; 12266</t>
+          <t>2777; 12613</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3072; 14048</t>
+          <t>2986; 13475</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2060; 12173</t>
+          <t>2050; 11793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>453; 5268</t>
+          <t>443; 5736</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4676; 20145</t>
+          <t>4520; 17971</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5098; 17715</t>
+          <t>5041; 18014</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6072; 21939</t>
+          <t>5714; 20789</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2656; 10092</t>
+          <t>2961; 11083</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9305; 25679</t>
+          <t>9712; 26454</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10169; 27096</t>
+          <t>10305; 27944</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10208; 27410</t>
+          <t>10125; 27768</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3796; 12284</t>
+          <t>4358; 13931</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31015</t>
+          <t>32858</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>34038</t>
+          <t>37722</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>65053</t>
+          <t>70580</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13659; 31464</t>
+          <t>13592; 32020</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15598; 39378</t>
+          <t>15737; 37196</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23198; 46846</t>
+          <t>22148; 48666</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19033; 49086</t>
+          <t>19978; 46823</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16751; 37271</t>
+          <t>16606; 37312</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7029; 22617</t>
+          <t>7468; 24132</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20004; 43245</t>
+          <t>19555; 42600</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23045; 48195</t>
+          <t>27697; 49857</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34475; 61905</t>
+          <t>33641; 60633</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26924; 55189</t>
+          <t>26684; 53610</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48387; 82468</t>
+          <t>47770; 79313</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>49297; 82646</t>
+          <t>56192; 91095</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26462</t>
+          <t>29111</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39234</t>
+          <t>41138</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65696</t>
+          <t>70249</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11236; 30173</t>
+          <t>11025; 29312</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6068; 22204</t>
+          <t>6171; 22741</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14137; 34234</t>
+          <t>13982; 35110</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16898; 38478</t>
+          <t>17837; 41083</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11740; 30217</t>
+          <t>11714; 30188</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11850; 31280</t>
+          <t>11937; 31056</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14981; 35906</t>
+          <t>15456; 35320</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29914; 50755</t>
+          <t>31503; 52465</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26606; 53424</t>
+          <t>27854; 54127</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21503; 47839</t>
+          <t>20884; 46482</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34156; 62266</t>
+          <t>34174; 62361</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>52329; 83268</t>
+          <t>56041; 87044</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59406</t>
+          <t>64044</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>78670</t>
+          <t>84657</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>138076</t>
+          <t>148701</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33614; 62190</t>
+          <t>34362; 63320</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31602; 62766</t>
+          <t>31062; 60710</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47548; 78161</t>
+          <t>46901; 80150</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42503; 81572</t>
+          <t>48481; 83413</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42750; 74119</t>
+          <t>41285; 70942</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31069; 58840</t>
+          <t>31642; 59077</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50252; 85022</t>
+          <t>49781; 85171</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>63023; 97345</t>
+          <t>70493; 101416</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>81811; 123182</t>
+          <t>83428; 124147</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>69553; 107044</t>
+          <t>70402; 107402</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>106812; 153311</t>
+          <t>104625; 151774</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>112573; 166125</t>
+          <t>125962; 175557</t>
         </is>
       </c>
     </row>
